--- a/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_RV__IC50.xlsx
+++ b/examples/LargeDrugCombo_Goetz_Cancers_2024/tables/data__sa_fit_heat_RV__IC50.xlsx
@@ -381,59 +381,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2">
-        <v>0.8104864698307858</v>
-      </c>
-      <c r="C2">
-        <v>0.1382922591412536</v>
+        <v>1.049232832500666</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D2">
-        <v>0.01150059371847246</v>
+        <v>0.02183280094671765</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3">
-        <v>0.3163115314858597</v>
+        <v>2.165292212915793</v>
       </c>
       <c r="C3">
-        <v>0.1870256832456715</v>
+        <v>0.6745844813927772</v>
       </c>
       <c r="D3">
-        <v>0.01291205885613602</v>
+        <v>0.05717077646540165</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4">
-        <v>3.272672292192316</v>
+        <v>0.6746785390375528</v>
       </c>
       <c r="C4">
-        <v>0.5136446664412255</v>
+        <v>0.2244141544643958</v>
       </c>
       <c r="D4">
-        <v>0.04628737697791888</v>
+        <v>0.0175820441483356</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>1.549142737495342</v>
+          <t>A-253</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -441,49 +445,53 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0273691722214859</v>
+        <v>0.3892026462101866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6">
-        <v>0.6746785390375528</v>
+        <v>0.2927635393263717</v>
       </c>
       <c r="C6">
-        <v>0.2244141544643958</v>
+        <v>0.1240033904285402</v>
       </c>
       <c r="D6">
-        <v>0.0175820441483356</v>
+        <v>0.01030940405027802</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2.165292212915793</v>
-      </c>
-      <c r="C7">
-        <v>0.6745844813927772</v>
+          <t>A-431</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D7">
-        <v>0.05717077646540165</v>
+        <v>0.2613993056252913</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8">
-        <v>38.45408202119784</v>
+        <v>23.67514858539014</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -491,501 +499,501 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.3958276734798155</v>
+        <v>0.06805935074551207</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9">
-        <v>0.377634036257278</v>
-      </c>
-      <c r="C9">
-        <v>0.1747820212336745</v>
+        <v>12.38366222487715</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D9">
-        <v>0.01153973193766984</v>
+        <v>0.7204405186226147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10">
-        <v>5.318950107621514</v>
+        <v>0.7488245725371083</v>
       </c>
       <c r="C10">
-        <v>0.7417657245565678</v>
+        <v>0.1780653835193772</v>
       </c>
       <c r="D10">
-        <v>0.1012482655633648</v>
+        <v>0.01326035882719153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>COLO 829</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>0.8104864698307858</v>
+      </c>
+      <c r="C11">
+        <v>0.1382922591412536</v>
       </c>
       <c r="D11">
-        <v>0.2613993056252913</v>
+        <v>0.01150059371847246</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.2927635393263717</v>
+        <v>1.611535491949094</v>
       </c>
       <c r="C12">
-        <v>0.1240033904285402</v>
+        <v>0.2182326924043154</v>
       </c>
       <c r="D12">
-        <v>0.01030940405027802</v>
+        <v>0.02436830227051887</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13">
-        <v>1.049232832500666</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.6940119436702878</v>
+      </c>
+      <c r="C13">
+        <v>0.154674651309886</v>
       </c>
       <c r="D13">
-        <v>0.02183280094671765</v>
+        <v>0.01342398085779387</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>COLO 857</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>0.2751978396697531</v>
       </c>
       <c r="C14">
-        <v>0.1128395374641439</v>
+        <v>0.1275572130865616</v>
       </c>
       <c r="D14">
-        <v>0.04898076420339947</v>
+        <v>0.009090560622807858</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15">
-        <v>15.83647771684941</v>
+        <v>0.2604280301219367</v>
       </c>
       <c r="C15">
-        <v>0.1633823636065891</v>
+        <v>0.0947154382551388</v>
       </c>
       <c r="D15">
-        <v>0.1070972831925886</v>
+        <v>0.007993303999109002</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>G-361</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>0.377634036257278</v>
       </c>
       <c r="C16">
-        <v>0.07777020612824302</v>
+        <v>0.1747820212336745</v>
       </c>
       <c r="D16">
-        <v>0.03338419857762398</v>
+        <v>0.01153973193766984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>HCC1498</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>0.7266888452333375</v>
+      </c>
+      <c r="C17">
+        <v>0.07139140208212059</v>
       </c>
       <c r="D17">
-        <v>0.2483431705288865</v>
+        <v>0.01189173070831033</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18">
-        <v>0.7488245725371083</v>
+        <v>0.1680931020689742</v>
       </c>
       <c r="C18">
-        <v>0.1780653835193772</v>
+        <v>0.09476362033853895</v>
       </c>
       <c r="D18">
-        <v>0.01326035882719153</v>
+        <v>0.009963535690507107</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>0.5964848375243496</v>
-      </c>
-      <c r="C19">
-        <v>0.1926292523334292</v>
+          <t>HSC-1</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D19">
-        <v>0.01512329694805864</v>
+        <v>10.40871645855476</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20">
-        <v>0.185074901595573</v>
-      </c>
-      <c r="C20">
-        <v>0.09750893988194143</v>
+        <v>13.5538482933805</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D20">
-        <v>0.005252785087124888</v>
+        <v>0.1030565080872861</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21">
-        <v>0.2839410775519471</v>
+        <v>0.7450871632694995</v>
       </c>
       <c r="C21">
-        <v>0.1028777861030668</v>
+        <v>0.158316237551891</v>
       </c>
       <c r="D21">
-        <v>0.006703906381770702</v>
+        <v>0.02435280590379038</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22">
-        <v>1.611535491949094</v>
+        <v>5.318950107621514</v>
       </c>
       <c r="C22">
-        <v>0.2182326924043154</v>
+        <v>0.7417657245565678</v>
       </c>
       <c r="D22">
-        <v>0.02436830227051887</v>
+        <v>0.1012482655633648</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23">
-        <v>23.67514858539014</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>3.272672292192316</v>
+      </c>
+      <c r="C23">
+        <v>0.5136446664412255</v>
       </c>
       <c r="D23">
-        <v>0.06805935074551207</v>
+        <v>0.04628737697791888</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
-        </is>
-      </c>
-      <c r="B24">
-        <v>25.20258967123168</v>
-      </c>
-      <c r="C24">
-        <v>0.07488229414872549</v>
+          <t>Hs 852.T</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D24">
-        <v>0.007881165920623353</v>
+        <v>0.2483431705288865</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25">
-        <v>0.207267275245631</v>
-      </c>
-      <c r="C25">
-        <v>0.06810376906361958</v>
+        <v>2.543197799007975</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D25">
-        <v>0.01655053921641816</v>
+        <v>0.0602861152020563</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
-        </is>
-      </c>
-      <c r="B26">
-        <v>0.5282950314584663</v>
-      </c>
-      <c r="C26">
-        <v>0.1380382726660192</v>
+          <t>IGR-39</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D26">
-        <v>0.01484634735514432</v>
+        <v>3.594688068955991</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.3651990010856769</v>
-      </c>
-      <c r="C27">
-        <v>0.06556522485864745</v>
+        <v>1.549142737495342</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D27">
-        <v>0.005111051323905777</v>
+        <v>0.0273691722214859</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28">
-        <v>2.543197799007975</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.5282950314584663</v>
+      </c>
+      <c r="C28">
+        <v>0.1380382726660192</v>
       </c>
       <c r="D28">
-        <v>0.0602861152020563</v>
+        <v>0.01484634735514432</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>MEL-JUSO</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>15.83647771684941</v>
+      </c>
+      <c r="C29">
+        <v>0.1633823636065891</v>
       </c>
       <c r="D29">
-        <v>3.594688068955991</v>
+        <v>0.1070972831925886</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30">
-        <v>0.6940119436702878</v>
+        <v>0.5568337276440459</v>
       </c>
       <c r="C30">
-        <v>0.154674651309886</v>
+        <v>0.1092981386444873</v>
       </c>
       <c r="D30">
-        <v>0.01342398085779387</v>
+        <v>0.007893281161722911</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31">
-        <v>0.2751978396697531</v>
-      </c>
-      <c r="C31">
-        <v>0.1275572130865616</v>
+        <v>38.45408202119784</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D31">
-        <v>0.009090560622807858</v>
+        <v>0.3958276734798155</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32">
-        <v>0.1680931020689742</v>
+        <v>0.2141293181794042</v>
       </c>
       <c r="C32">
-        <v>0.09476362033853895</v>
+        <v>0.08288694201825846</v>
       </c>
       <c r="D32">
-        <v>0.009963535690507107</v>
+        <v>0.005794131633411018</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33">
-        <v>0.5568337276440459</v>
+        <v>0.5964848375243496</v>
       </c>
       <c r="C33">
-        <v>0.1092981386444873</v>
+        <v>0.1926292523334292</v>
       </c>
       <c r="D33">
-        <v>0.007893281161722911</v>
+        <v>0.01512329694805864</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
-        </is>
-      </c>
-      <c r="B34">
-        <v>0.5136386417380484</v>
+          <t>SK-MEL-2</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="C34">
-        <v>0.1321910238279665</v>
+        <v>0.1128395374641439</v>
       </c>
       <c r="D34">
-        <v>0.02050724793951618</v>
+        <v>0.04898076420339947</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35">
-        <v>0.2141293181794042</v>
+        <v>0.2839410775519471</v>
       </c>
       <c r="C35">
-        <v>0.08288694201825846</v>
+        <v>0.1028777861030668</v>
       </c>
       <c r="D35">
-        <v>0.005794131633411018</v>
+        <v>0.006703906381770702</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36">
-        <v>0.2604280301219367</v>
+        <v>0.3163115314858597</v>
       </c>
       <c r="C36">
-        <v>0.0947154382551388</v>
+        <v>0.1870256832456715</v>
       </c>
       <c r="D36">
-        <v>0.007993303999109002</v>
+        <v>0.01291205885613602</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37">
-        <v>13.5538482933805</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.5136386417380484</v>
+      </c>
+      <c r="C37">
+        <v>0.1321910238279665</v>
       </c>
       <c r="D37">
-        <v>0.1030565080872861</v>
+        <v>0.02050724793951618</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -993,117 +1001,109 @@
           <t>Inf</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+      <c r="C38">
+        <v>0.07777020612824302</v>
       </c>
       <c r="D38">
-        <v>10.40871645855476</v>
+        <v>0.03338419857762398</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39">
-        <v>0.8499003305388566</v>
-      </c>
-      <c r="C39">
-        <v>0.2563573917092837</v>
+        <v>5.341267144588686</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
       </c>
       <c r="D39">
-        <v>0.02416618832618581</v>
+        <v>0.07470241833599801</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40">
-        <v>5.341267144588686</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>25.20258967123168</v>
+      </c>
+      <c r="C40">
+        <v>0.07488229414872549</v>
       </c>
       <c r="D40">
-        <v>0.07470241833599801</v>
+        <v>0.007881165920623353</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41">
-        <v>0.7266888452333375</v>
+        <v>0.8499003305388566</v>
       </c>
       <c r="C41">
-        <v>0.07139140208212059</v>
+        <v>0.2563573917092837</v>
       </c>
       <c r="D41">
-        <v>0.01189173070831033</v>
+        <v>0.02416618832618581</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+          <t>UACC-62</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>0.185074901595573</v>
+      </c>
+      <c r="C42">
+        <v>0.09750893988194143</v>
       </c>
       <c r="D42">
-        <v>0.3892026462101866</v>
+        <v>0.005252785087124888</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43">
-        <v>0.7450871632694995</v>
+        <v>0.207267275245631</v>
       </c>
       <c r="C43">
-        <v>0.158316237551891</v>
+        <v>0.06810376906361958</v>
       </c>
       <c r="D43">
-        <v>0.02435280590379038</v>
+        <v>0.01655053921641816</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44">
-        <v>12.38366222487715</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.3651990010856769</v>
+      </c>
+      <c r="C44">
+        <v>0.06556522485864745</v>
       </c>
       <c r="D44">
-        <v>0.7204405186226147</v>
+        <v>0.005111051323905777</v>
       </c>
     </row>
   </sheetData>
@@ -1131,7 +1131,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>COLO 829</t>
+          <t>501A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +1143,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SK-MEL-28</t>
+          <t>624 mel</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hs 695T</t>
+          <t>928 mel</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1167,7 +1167,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MDA-MB-435</t>
+          <t>A-253</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1179,7 +1179,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>928 mel</t>
+          <t>A-375</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1191,7 +1191,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>624 mel</t>
+          <t>A-431</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1203,7 +1203,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>RPMI-7951</t>
+          <t>A2058</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G-361</t>
+          <t>A388</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1227,7 +1227,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hs 294T</t>
+          <t>COLO 800</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1239,7 +1239,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A-431</t>
+          <t>COLO 829</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1251,7 +1251,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A-375</t>
+          <t>COLO 849</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>501A</t>
+          <t>COLO 853</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK-MEL-2</t>
+          <t>COLO 857</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1287,7 +1287,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MEL-JUSO</t>
+          <t>COLO 858</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SK-MEL-30</t>
+          <t>G-361</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1311,7 +1311,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Hs 852.T</t>
+          <t>HCC1498</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1323,7 +1323,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COLO 800</t>
+          <t>HMY-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SK-MEL-1</t>
+          <t>HSC-1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UACC-62</t>
+          <t>HSC-5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1359,7 +1359,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SK-MEL-24</t>
+          <t>HT-144</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>COLO 849</t>
+          <t>Hs 294T</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A2058</t>
+          <t>Hs 695T</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1395,7 +1395,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SK23-mel</t>
+          <t>Hs 852.T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1407,7 +1407,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UCSD-242l</t>
+          <t>IGR-1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MEL-HO</t>
+          <t>IGR-39</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1431,7 +1431,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>WM-266-4</t>
+          <t>MDA-MB-435</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1443,7 +1443,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IGR-1</t>
+          <t>MEL-HO</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IGR-39</t>
+          <t>MEL-JUSO</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>COLO 853</t>
+          <t>MMAc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1479,7 +1479,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>COLO 857</t>
+          <t>RPMI-7951</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1491,7 +1491,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>HMY-1</t>
+          <t>RVH-421</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1503,7 +1503,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MMAc</t>
+          <t>SK-MEL-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1515,7 +1515,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SK-MEL-3</t>
+          <t>SK-MEL-2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1527,7 +1527,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RVH-421</t>
+          <t>SK-MEL-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1539,7 +1539,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>COLO 858</t>
+          <t>SK-MEL-28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HSC-5</t>
+          <t>SK-MEL-3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HSC-1</t>
+          <t>SK-MEL-30</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UACC-257</t>
+          <t>SK-MEL-31</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1587,7 +1587,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SK-MEL-31</t>
+          <t>SK23-mel</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1599,7 +1599,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HCC1498</t>
+          <t>UACC-257</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1611,7 +1611,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A-253</t>
+          <t>UACC-62</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1623,7 +1623,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HT-144</t>
+          <t>UCSD-242l</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1635,7 +1635,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A388</t>
+          <t>WM-266-4</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
